--- a/database/event/5730/event_5730_evp_summary.xlsx
+++ b/database/event/5730/event_5730_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.342499999999999</v>
+        <v>8.3154</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1045</v>
+        <v>4.0912</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9488</v>
+        <v>2.8689</v>
       </c>
       <c r="E2" t="n">
-        <v>8.342499999999999</v>
+        <v>8.3154</v>
       </c>
       <c r="F2" t="n">
-        <v>1.826</v>
+        <v>1.7989</v>
       </c>
       <c r="G2" t="n">
         <v>6.5165</v>
       </c>
       <c r="H2" t="n">
-        <v>1.826</v>
+        <v>1.7989</v>
       </c>
       <c r="I2" t="n">
         <v>1.8602</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0296</v>
+        <v>6.1453</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9666</v>
+        <v>3.0235</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0145</v>
+        <v>2.0044</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0296</v>
+        <v>6.1453</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4126</v>
+        <v>4.5283</v>
       </c>
       <c r="G3" t="n">
         <v>1.617</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1924</v>
+        <v>5.6581</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2085</v>
+        <v>4.586</v>
       </c>
       <c r="J3" t="n">
         <v>1.617</v>
@@ -575,7 +575,7 @@
         <v>91</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8255</v>
+        <v>6.203</v>
       </c>
       <c r="N3" t="n">
         <v>264</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5981</v>
+        <v>6.0607</v>
       </c>
       <c r="C4" t="n">
-        <v>2.7543</v>
+        <v>2.9819</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8401</v>
+        <v>1.9707</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5981</v>
+        <v>6.0607</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9075</v>
+        <v>4.3701</v>
       </c>
       <c r="G4" t="n">
         <v>1.6906</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9075</v>
+        <v>4.5492</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9993</v>
+        <v>4.7439</v>
       </c>
       <c r="J4" t="n">
         <v>1.6906</v>
@@ -621,7 +621,7 @@
         <v>74</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6899</v>
+        <v>6.4345</v>
       </c>
       <c r="N4" t="n">
         <v>277</v>
@@ -640,7 +640,7 @@
         <v>2.4717</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6081</v>
+        <v>1.5576</v>
       </c>
       <c r="E5" t="n">
         <v>5.0238</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.684</v>
+        <v>4.9245</v>
       </c>
       <c r="C6" t="n">
-        <v>2.3045</v>
+        <v>2.4229</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4709</v>
+        <v>1.518</v>
       </c>
       <c r="E6" t="n">
-        <v>4.684</v>
+        <v>4.9245</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3612</v>
+        <v>4.6017</v>
       </c>
       <c r="G6" t="n">
         <v>0.3228</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5352</v>
+        <v>4.9124</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6418</v>
+        <v>5.1226</v>
       </c>
       <c r="J6" t="n">
         <v>0.3228</v>
@@ -713,7 +713,7 @@
         <v>82</v>
       </c>
       <c r="M6" t="n">
-        <v>4.9646</v>
+        <v>5.4454</v>
       </c>
       <c r="N6" t="n">
         <v>369</v>
@@ -722,81 +722,81 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3829</v>
+        <v>4.7479</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1564</v>
+        <v>2.336</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3492</v>
+        <v>1.4477</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3829</v>
+        <v>4.7479</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2051</v>
+        <v>4.0688</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1778</v>
+        <v>0.6791</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3578</v>
+        <v>4.0768</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5321</v>
+        <v>4.2513</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1778</v>
+        <v>0.6791</v>
       </c>
       <c r="K7" t="n">
-        <v>153</v>
+        <v>203</v>
       </c>
       <c r="L7" t="n">
-        <v>58</v>
+        <v>246</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7099</v>
+        <v>4.9304</v>
       </c>
       <c r="N7" t="n">
-        <v>211</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2998</v>
+        <v>4.3829</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1155</v>
+        <v>2.1564</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3157</v>
+        <v>1.3022</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2998</v>
+        <v>4.3829</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4444</v>
+        <v>4.2051</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1446</v>
+        <v>0.1778</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3205</v>
+        <v>4.3578</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3124</v>
+        <v>3.5321</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1446</v>
+        <v>0.1778</v>
       </c>
       <c r="K8" t="n">
         <v>153</v>
@@ -805,7 +805,7 @@
         <v>58</v>
       </c>
       <c r="M8" t="n">
-        <v>4.167800000000001</v>
+        <v>3.7099</v>
       </c>
       <c r="N8" t="n">
         <v>211</v>
@@ -814,47 +814,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1387</v>
+        <v>4.3119</v>
       </c>
       <c r="C9" t="n">
-        <v>2.0362</v>
+        <v>2.1215</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2506</v>
+        <v>1.274</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1387</v>
+        <v>4.3119</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4596</v>
+        <v>4.4565</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6791</v>
+        <v>-0.1446</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4596</v>
+        <v>5.3692</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5409</v>
+        <v>4.3519</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6791</v>
+        <v>-0.1446</v>
       </c>
       <c r="K9" t="n">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="L9" t="n">
-        <v>246</v>
+        <v>58</v>
       </c>
       <c r="M9" t="n">
-        <v>4.220000000000001</v>
+        <v>4.2073</v>
       </c>
       <c r="N9" t="n">
-        <v>449</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4007</v>
+        <v>3.629</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6732</v>
+        <v>1.7855</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9524</v>
+        <v>1.0019</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4007</v>
+        <v>3.629</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4934</v>
+        <v>0.7217</v>
       </c>
       <c r="G10" t="n">
         <v>2.9073</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4934</v>
+        <v>0.7217</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5027</v>
+        <v>0.7463</v>
       </c>
       <c r="J10" t="n">
         <v>2.9073</v>
@@ -897,7 +897,7 @@
         <v>221</v>
       </c>
       <c r="M10" t="n">
-        <v>3.41</v>
+        <v>3.6536</v>
       </c>
       <c r="N10" t="n">
         <v>388</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0021</v>
+        <v>2.9501</v>
       </c>
       <c r="C11" t="n">
-        <v>1.477</v>
+        <v>1.4515</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7914</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0021</v>
+        <v>2.9501</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8087</v>
+        <v>2.7567</v>
       </c>
       <c r="G11" t="n">
         <v>0.1934</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8087</v>
+        <v>2.7567</v>
       </c>
       <c r="I11" t="n">
         <v>2.8747</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5497</v>
+        <v>2.8546</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2545</v>
+        <v>1.4045</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6087</v>
+        <v>0.6934</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5497</v>
+        <v>2.8546</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8066</v>
+        <v>2.7512</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2569</v>
+        <v>0.1034</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8066</v>
+        <v>2.7512</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2748</v>
+        <v>2.845</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2569</v>
+        <v>0.1034</v>
       </c>
       <c r="K12" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="L12" t="n">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0179</v>
+        <v>2.9484</v>
       </c>
       <c r="N12" t="n">
-        <v>211</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4548</v>
+        <v>2.5497</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2078</v>
+        <v>1.2545</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5703</v>
+        <v>0.5719</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4548</v>
+        <v>2.5497</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3514</v>
+        <v>2.8066</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1034</v>
+        <v>-0.2569</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3514</v>
+        <v>2.8066</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3955</v>
+        <v>2.2748</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1034</v>
+        <v>-0.2569</v>
       </c>
       <c r="K13" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="L13" t="n">
-        <v>221</v>
+        <v>58</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4989</v>
+        <v>2.0179</v>
       </c>
       <c r="N13" t="n">
-        <v>388</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14">
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3243</v>
+        <v>2.2984</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1436</v>
+        <v>1.1308</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4718</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3243</v>
+        <v>2.2984</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3243</v>
+        <v>2.2984</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3243</v>
+        <v>2.2984</v>
       </c>
       <c r="I14" t="n">
         <v>2.3569</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2364</v>
+        <v>2.2115</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1003</v>
+        <v>1.0881</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4821</v>
+        <v>0.4372</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2364</v>
+        <v>2.2115</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2364</v>
+        <v>2.2115</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2364</v>
+        <v>2.2115</v>
       </c>
       <c r="I15" t="n">
         <v>2.2678</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0013</v>
+        <v>1.9858</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9846</v>
+        <v>0.977</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3871</v>
+        <v>0.3472</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0013</v>
+        <v>1.9858</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3883</v>
+        <v>1.3728</v>
       </c>
       <c r="G16" t="n">
         <v>0.613</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3883</v>
+        <v>1.3728</v>
       </c>
       <c r="I16" t="n">
         <v>1.4078</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.973</v>
+        <v>1.951</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9707</v>
+        <v>0.9599</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3757</v>
+        <v>0.3334</v>
       </c>
       <c r="E17" t="n">
-        <v>1.973</v>
+        <v>1.951</v>
       </c>
       <c r="F17" t="n">
-        <v>1.973</v>
+        <v>1.951</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.973</v>
+        <v>1.951</v>
       </c>
       <c r="I17" t="n">
         <v>2.0007</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.676</v>
+        <v>1.7992</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8246</v>
+        <v>0.8852</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2557</v>
+        <v>0.2729</v>
       </c>
       <c r="E18" t="n">
-        <v>1.676</v>
+        <v>1.7992</v>
       </c>
       <c r="F18" t="n">
-        <v>1.676</v>
+        <v>1.7992</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.676</v>
+        <v>1.7992</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6995</v>
+        <v>1.845</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6995</v>
+        <v>1.845</v>
       </c>
       <c r="N18" t="n">
         <v>197</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6671</v>
+        <v>1.6547</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8202</v>
+        <v>0.8141</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2521</v>
+        <v>0.2153</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6671</v>
+        <v>1.6547</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6671</v>
+        <v>1.6547</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6671</v>
+        <v>1.6547</v>
       </c>
       <c r="I19" t="n">
         <v>1.6827</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6415</v>
+        <v>1.632</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8076</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2418</v>
+        <v>0.2063</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6415</v>
+        <v>1.632</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5113</v>
+        <v>0.5018</v>
       </c>
       <c r="G20" t="n">
         <v>1.1302</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5113</v>
+        <v>0.5018</v>
       </c>
       <c r="I20" t="n">
         <v>0.5233</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5522</v>
+        <v>1.5349</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7637</v>
+        <v>0.7552</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2057</v>
+        <v>0.1676</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5522</v>
+        <v>1.5349</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5522</v>
+        <v>1.5349</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5522</v>
+        <v>1.5349</v>
       </c>
       <c r="I21" t="n">
         <v>1.574</v>
@@ -1412,265 +1412,265 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4222</v>
+        <v>1.5147</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6997</v>
+        <v>0.7452</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1532</v>
+        <v>0.1595</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4222</v>
+        <v>1.5147</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4222</v>
+        <v>1.5147</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4222</v>
+        <v>1.5147</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4422</v>
+        <v>1.5533</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4422</v>
+        <v>1.5533</v>
       </c>
       <c r="N22" t="n">
-        <v>162</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3644</v>
+        <v>1.4288</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6713</v>
+        <v>0.703</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1298</v>
+        <v>0.1253</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3644</v>
+        <v>1.4288</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8928</v>
+        <v>1.4288</v>
       </c>
       <c r="G23" t="n">
-        <v>2.2571</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8928</v>
+        <v>1.4288</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9095</v>
+        <v>1.4652</v>
       </c>
       <c r="J23" t="n">
-        <v>2.2571</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="L23" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3476</v>
+        <v>1.4652</v>
       </c>
       <c r="N23" t="n">
-        <v>388</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3643</v>
+        <v>1.4064</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6712</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1298</v>
+        <v>0.1164</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3643</v>
+        <v>1.4064</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3643</v>
+        <v>1.4064</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3643</v>
+        <v>1.4064</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3963</v>
+        <v>1.4422</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>265</v>
+        <v>162</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3963</v>
+        <v>1.4422</v>
       </c>
       <c r="N24" t="n">
-        <v>265</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3248</v>
+        <v>1.3776</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6518</v>
+        <v>0.6778</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1138</v>
+        <v>0.1049</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3248</v>
+        <v>1.3776</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3248</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2.2571</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3248</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3434</v>
+        <v>-0.9095</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2.2571</v>
       </c>
       <c r="K25" t="n">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3434</v>
+        <v>1.3476</v>
       </c>
       <c r="N25" t="n">
-        <v>180</v>
+        <v>388</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3146</v>
+        <v>1.339</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6468</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1097</v>
+        <v>0.0895</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3146</v>
+        <v>1.339</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3146</v>
+        <v>1.339</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3146</v>
+        <v>1.339</v>
       </c>
       <c r="I26" t="n">
-        <v>1.333</v>
+        <v>1.3963</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.333</v>
+        <v>1.3963</v>
       </c>
       <c r="N26" t="n">
-        <v>205</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8901</v>
+        <v>1.239</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4379</v>
+        <v>0.6096</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0618</v>
+        <v>0.0497</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8901</v>
+        <v>1.239</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6133999999999999</v>
+        <v>1.4652</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2767</v>
+        <v>-0.2262</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6133999999999999</v>
+        <v>1.4652</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6278</v>
+        <v>1.5279</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2767</v>
+        <v>-0.2262</v>
       </c>
       <c r="K27" t="n">
         <v>287</v>
@@ -1679,7 +1679,7 @@
         <v>82</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9045000000000001</v>
+        <v>1.3017</v>
       </c>
       <c r="N27" t="n">
         <v>369</v>
@@ -1688,369 +1688,369 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DANK1NG</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8287</v>
+        <v>0.8787</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4077</v>
+        <v>0.4323</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0866</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8287</v>
+        <v>0.8787</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8287</v>
+        <v>0.602</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.2767</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8287</v>
+        <v>0.602</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8287</v>
+        <v>0.6278</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.2767</v>
       </c>
       <c r="K28" t="n">
-        <v>81</v>
+        <v>287</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8287</v>
+        <v>0.9045000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>81</v>
+        <v>369</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8138</v>
+        <v>0.8632</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4004</v>
+        <v>0.4247</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0926</v>
+        <v>-0.1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8138</v>
+        <v>0.8632</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8138</v>
+        <v>0.8632</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8138</v>
+        <v>0.8632</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8329</v>
+        <v>0.8852</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>265</v>
+        <v>180</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8329</v>
+        <v>0.8852</v>
       </c>
       <c r="N29" t="n">
-        <v>265</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>DANK1NG</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7722</v>
+        <v>0.8287</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3799</v>
+        <v>0.4077</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1094</v>
+        <v>-0.1138</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7722</v>
+        <v>0.8287</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7722</v>
+        <v>0.8287</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7722</v>
+        <v>0.8287</v>
       </c>
       <c r="I30" t="n">
-        <v>0.783</v>
+        <v>0.8287</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.783</v>
+        <v>0.8287</v>
       </c>
       <c r="N30" t="n">
-        <v>180</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7089</v>
+        <v>0.7987</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3488</v>
+        <v>0.393</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.135</v>
+        <v>-0.1257</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7089</v>
+        <v>0.7987</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7089</v>
+        <v>0.7987</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7089</v>
+        <v>0.7987</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7189</v>
+        <v>0.8329</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>180</v>
+        <v>265</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7189</v>
+        <v>0.8329</v>
       </c>
       <c r="N31" t="n">
-        <v>180</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6909</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3399</v>
+        <v>0.3757</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1423</v>
+        <v>-0.1397</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6909</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6909</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6909</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6909</v>
+        <v>0.783</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>88</v>
+        <v>180</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6909</v>
+        <v>0.783</v>
       </c>
       <c r="N32" t="n">
-        <v>88</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6617</v>
+        <v>0.7632</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3256</v>
+        <v>0.3755</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1541</v>
+        <v>-0.1399</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6617</v>
+        <v>0.7632</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6617</v>
+        <v>0.7632</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6617</v>
+        <v>0.7632</v>
       </c>
       <c r="I33" t="n">
-        <v>0.671</v>
+        <v>0.7632</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.671</v>
+        <v>0.7632</v>
       </c>
       <c r="N33" t="n">
-        <v>162</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5792</v>
+        <v>0.6543</v>
       </c>
       <c r="C34" t="n">
-        <v>0.285</v>
+        <v>0.3219</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1874</v>
+        <v>-0.1832</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5792</v>
+        <v>0.6543</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5792</v>
+        <v>0.6543</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5792</v>
+        <v>0.6543</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5792</v>
+        <v>0.671</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5792</v>
+        <v>0.671</v>
       </c>
       <c r="N34" t="n">
-        <v>83</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5736</v>
+        <v>0.5792</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2822</v>
+        <v>0.285</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1896</v>
+        <v>-0.2132</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5736</v>
+        <v>0.5792</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7998</v>
+        <v>0.5792</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2262</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7998</v>
+        <v>0.5792</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8186</v>
+        <v>0.5792</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2262</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="L35" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5924</v>
+        <v>0.5792</v>
       </c>
       <c r="N35" t="n">
-        <v>369</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36">
@@ -2066,7 +2066,7 @@
         <v>0.2791</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1922</v>
+        <v>-0.2179</v>
       </c>
       <c r="E36" t="n">
         <v>0.5673</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5091</v>
+        <v>0.5053</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2505</v>
+        <v>0.2486</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2157</v>
+        <v>-0.2426</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5091</v>
+        <v>0.5053</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5091</v>
+        <v>0.5053</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5091</v>
+        <v>0.5053</v>
       </c>
       <c r="I37" t="n">
         <v>0.5138</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4792</v>
+        <v>0.4738</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2358</v>
+        <v>0.2331</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2278</v>
+        <v>-0.2551</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4792</v>
+        <v>0.4738</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4792</v>
+        <v>0.4738</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4792</v>
+        <v>0.4738</v>
       </c>
       <c r="I38" t="n">
         <v>0.4859</v>
@@ -2204,7 +2204,7 @@
         <v>0.2189</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2416</v>
+        <v>-0.2666</v>
       </c>
       <c r="E39" t="n">
         <v>0.445</v>
@@ -2250,7 +2250,7 @@
         <v>0.1693</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2824</v>
+        <v>-0.3068</v>
       </c>
       <c r="E40" t="n">
         <v>0.3441</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.2873</v>
+        <v>0.282</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1414</v>
+        <v>0.1387</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3053</v>
+        <v>-0.3316</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2873</v>
+        <v>0.282</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2873</v>
+        <v>0.282</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2873</v>
+        <v>0.282</v>
       </c>
       <c r="I41" t="n">
         <v>0.2941</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2746</v>
+        <v>0.271</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1351</v>
+        <v>0.1333</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3104</v>
+        <v>-0.3359</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2746</v>
+        <v>0.271</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3267</v>
+        <v>0.3231</v>
       </c>
       <c r="G42" t="n">
         <v>-0.0521</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3267</v>
+        <v>0.3231</v>
       </c>
       <c r="I42" t="n">
         <v>0.3313</v>
@@ -2388,7 +2388,7 @@
         <v>0.1248</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3189</v>
+        <v>-0.3429</v>
       </c>
       <c r="E43" t="n">
         <v>0.2536</v>
@@ -2434,7 +2434,7 @@
         <v>0.1084</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3323</v>
+        <v>-0.3561</v>
       </c>
       <c r="E44" t="n">
         <v>0.2204</v>
@@ -2480,7 +2480,7 @@
         <v>0.0827</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3535</v>
+        <v>-0.3769</v>
       </c>
       <c r="E45" t="n">
         <v>0.1681</v>
@@ -2526,7 +2526,7 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3615</v>
+        <v>-0.3849</v>
       </c>
       <c r="E46" t="n">
         <v>0.1482</v>
@@ -2572,7 +2572,7 @@
         <v>0.0538</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3772</v>
+        <v>-0.4003</v>
       </c>
       <c r="E47" t="n">
         <v>0.1094</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0925</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0455</v>
+        <v>0.0447</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.384</v>
+        <v>-0.4077</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0925</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0925</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0925</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="I48" t="n">
         <v>0.09470000000000001</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0761</v>
+        <v>0.0687</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0374</v>
+        <v>0.0338</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3906</v>
+        <v>-0.4165</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0761</v>
+        <v>0.0687</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4034</v>
+        <v>0.396</v>
       </c>
       <c r="G49" t="n">
         <v>-0.3273</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4034</v>
+        <v>0.396</v>
       </c>
       <c r="I49" t="n">
         <v>0.4129</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0591</v>
+        <v>0.0584</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0291</v>
+        <v>0.0287</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3975</v>
+        <v>-0.4206</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0591</v>
+        <v>0.0584</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0591</v>
+        <v>0.0584</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0591</v>
+        <v>0.0584</v>
       </c>
       <c r="I50" t="n">
         <v>0.0599</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0453</v>
+        <v>0.0482</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0223</v>
+        <v>0.0237</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4031</v>
+        <v>-0.4247</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0453</v>
+        <v>0.0482</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2584</v>
+        <v>-0.2555</v>
       </c>
       <c r="G51" t="n">
         <v>0.3037</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2584</v>
+        <v>-0.2555</v>
       </c>
       <c r="I51" t="n">
         <v>-0.262</v>
@@ -2802,7 +2802,7 @@
         <v>0.0081</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4147</v>
+        <v>-0.4373</v>
       </c>
       <c r="E52" t="n">
         <v>0.0165</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0123</v>
+        <v>-0.0122</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0061</v>
+        <v>-0.006</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4263</v>
+        <v>-0.4488</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0123</v>
+        <v>-0.0122</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0123</v>
+        <v>-0.0122</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0123</v>
+        <v>-0.0122</v>
       </c>
       <c r="I53" t="n">
         <v>-0.0125</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0214</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4389</v>
+        <v>-0.4612</v>
       </c>
       <c r="E54" t="n">
         <v>-0.0435</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0241</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4411</v>
+        <v>-0.4634</v>
       </c>
       <c r="E55" t="n">
         <v>-0.0489</v>
@@ -2976,277 +2976,277 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2538</v>
+        <v>-0.2476</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1249</v>
+        <v>-0.1218</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5239</v>
+        <v>-0.5426</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2538</v>
+        <v>-0.2476</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2538</v>
+        <v>-0.3629</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.1153</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2538</v>
+        <v>-0.3629</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2562</v>
+        <v>-0.3721</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>0.1153</v>
       </c>
       <c r="K56" t="n">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2562</v>
+        <v>-0.2568</v>
       </c>
       <c r="N56" t="n">
-        <v>115</v>
+        <v>237</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2663</v>
+        <v>-0.2519</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.131</v>
+        <v>-0.1239</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5289</v>
+        <v>-0.5443</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2663</v>
+        <v>-0.2519</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2663</v>
+        <v>-0.2519</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2663</v>
+        <v>-0.2519</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2663</v>
+        <v>-0.2562</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2663</v>
+        <v>-0.2562</v>
       </c>
       <c r="N57" t="n">
-        <v>81</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.295</v>
+        <v>-0.2663</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1451</v>
+        <v>-0.131</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5405</v>
+        <v>-0.55</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.295</v>
+        <v>-0.2663</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.6016</v>
+        <v>-0.2663</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3066</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.6016</v>
+        <v>-0.2663</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4876</v>
+        <v>-0.2663</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3066</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="L58" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.181</v>
+        <v>-0.2663</v>
       </c>
       <c r="N58" t="n">
-        <v>264</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.3038</v>
+        <v>-0.295</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1495</v>
+        <v>-0.1451</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5441</v>
+        <v>-0.5614</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3038</v>
+        <v>-0.295</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3038</v>
+        <v>-0.6016</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>0.3066</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3038</v>
+        <v>-0.6016</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3066</v>
+        <v>-0.4876</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>0.3066</v>
       </c>
       <c r="K59" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.3066</v>
+        <v>-0.181</v>
       </c>
       <c r="N59" t="n">
-        <v>115</v>
+        <v>264</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3133</v>
+        <v>-0.3015</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1541</v>
+        <v>-0.1483</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3133</v>
+        <v>-0.3015</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3133</v>
+        <v>-0.3015</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3133</v>
+        <v>-0.3015</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3133</v>
+        <v>-0.3066</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.3133</v>
+        <v>-0.3066</v>
       </c>
       <c r="N60" t="n">
-        <v>36</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3517</v>
+        <v>-0.3133</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.173</v>
+        <v>-0.1541</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5634</v>
+        <v>-0.5687</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3517</v>
+        <v>-0.3133</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.467</v>
+        <v>-0.3133</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1153</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.467</v>
+        <v>-0.3133</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4735</v>
+        <v>-0.3133</v>
       </c>
       <c r="J61" t="n">
-        <v>0.1153</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>163</v>
+        <v>36</v>
       </c>
       <c r="L61" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3582</v>
+        <v>-0.3133</v>
       </c>
       <c r="N61" t="n">
-        <v>237</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62">
@@ -3262,7 +3262,7 @@
         <v>-0.1771</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5668</v>
+        <v>-0.5873</v>
       </c>
       <c r="E62" t="n">
         <v>-0.3599</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3889</v>
+        <v>-0.3846</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1913</v>
+        <v>-0.1892</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.5785</v>
+        <v>-0.5971</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3889</v>
+        <v>-0.3846</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3889</v>
+        <v>-0.3846</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3889</v>
+        <v>-0.3846</v>
       </c>
       <c r="I63" t="n">
         <v>-0.3944</v>
@@ -3354,7 +3354,7 @@
         <v>-0.314</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6792</v>
+        <v>-0.6982</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6382</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.6512</v>
+        <v>-0.6439</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3204</v>
+        <v>-0.3168</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6844</v>
+        <v>-0.7004</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6512</v>
+        <v>-0.6439</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.6512</v>
+        <v>-0.6439</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.6512</v>
+        <v>-0.6439</v>
       </c>
       <c r="I65" t="n">
         <v>-0.6603</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7047</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3467</v>
+        <v>-0.338</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.706</v>
+        <v>-0.7176</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7047</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.9554</v>
+        <v>-0.9377</v>
       </c>
       <c r="G66" t="n">
         <v>0.2507</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.9554</v>
+        <v>-0.9377</v>
       </c>
       <c r="I66" t="n">
         <v>-0.9778</v>
@@ -3492,7 +3492,7 @@
         <v>-0.3814</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7345</v>
+        <v>-0.7527</v>
       </c>
       <c r="E67" t="n">
         <v>-0.7751</v>
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8976</v>
+        <v>-0.8758</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4416</v>
+        <v>-0.4309</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.784</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8976</v>
+        <v>-0.8758</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.9242</v>
+        <v>-0.9024</v>
       </c>
       <c r="G68" t="n">
         <v>0.0266</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.9242</v>
+        <v>-0.9024</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7491</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="J68" t="n">
         <v>0.0266</v>
@@ -3565,7 +3565,7 @@
         <v>58</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7225</v>
+        <v>-0.7048000000000001</v>
       </c>
       <c r="N68" t="n">
         <v>211</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.9559</v>
+        <v>-0.9382</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4703</v>
+        <v>-0.4616</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8075</v>
+        <v>-0.8177</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.9559</v>
+        <v>-0.9382</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9559</v>
+        <v>-0.9382</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.9559</v>
+        <v>-0.9382</v>
       </c>
       <c r="I69" t="n">
         <v>-0.9784</v>
@@ -3620,93 +3620,93 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.1962</v>
+        <v>-1.1925</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5885</v>
+        <v>-0.5867</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9046</v>
+        <v>-0.919</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.1962</v>
+        <v>-1.1925</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.1962</v>
+        <v>-1.1925</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.1962</v>
+        <v>-1.1925</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1962</v>
+        <v>-1.2229</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.1962</v>
+        <v>-1.2229</v>
       </c>
       <c r="N70" t="n">
-        <v>81</v>
+        <v>205</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.206</v>
+        <v>-1.1962</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5934</v>
+        <v>-0.5885</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9086</v>
+        <v>-0.9205</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.206</v>
+        <v>-1.1962</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.206</v>
+        <v>-1.1962</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.206</v>
+        <v>-1.1962</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2229</v>
+        <v>-1.1962</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.2229</v>
+        <v>-1.1962</v>
       </c>
       <c r="N71" t="n">
-        <v>205</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72">
@@ -3722,7 +3722,7 @@
         <v>-0.6036</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.917</v>
+        <v>-0.9327</v>
       </c>
       <c r="E72" t="n">
         <v>-1.2268</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6152</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9265</v>
+        <v>-0.9421</v>
       </c>
       <c r="E73" t="n">
         <v>-1.2505</v>
@@ -3804,93 +3804,93 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>doto</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.3612</v>
+        <v>-1.3479</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6697</v>
+        <v>-0.6632</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-0.9809</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.3612</v>
+        <v>-1.3479</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.3612</v>
+        <v>-1.3479</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.3612</v>
+        <v>-1.3479</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.3612</v>
+        <v>-1.3822</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.3612</v>
+        <v>-1.3822</v>
       </c>
       <c r="N74" t="n">
-        <v>92</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>doto</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.3631</v>
+        <v>-1.3612</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6706</v>
+        <v>-0.6697</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.972</v>
+        <v>-0.9862</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.3631</v>
+        <v>-1.3612</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.3631</v>
+        <v>-1.3612</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.3631</v>
+        <v>-1.3612</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.3822</v>
+        <v>-1.3612</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>162</v>
+        <v>92</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.3822</v>
+        <v>-1.3612</v>
       </c>
       <c r="N75" t="n">
-        <v>162</v>
+        <v>92</v>
       </c>
     </row>
     <row r="76">
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.426</v>
+        <v>-1.411</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7016</v>
+        <v>-0.6942</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9974</v>
+        <v>-1.0061</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.426</v>
+        <v>-1.411</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.8086</v>
+        <v>-0.7936</v>
       </c>
       <c r="G76" t="n">
         <v>-0.6173999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.8086</v>
+        <v>-0.7936</v>
       </c>
       <c r="I76" t="n">
         <v>-0.8276</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7149</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0083</v>
+        <v>-1.0228</v>
       </c>
       <c r="E77" t="n">
         <v>-1.453</v>
@@ -3998,7 +3998,7 @@
         <v>-0.7433</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0317</v>
+        <v>-1.0458</v>
       </c>
       <c r="E78" t="n">
         <v>-1.5108</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.5869</v>
+        <v>-1.5803</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.7808</v>
+        <v>-0.7775</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0624</v>
+        <v>-1.0735</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.5869</v>
+        <v>-1.5803</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.5869</v>
+        <v>-0.5803</v>
       </c>
       <c r="G79" t="n">
         <v>-1</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.5869</v>
+        <v>-0.5803</v>
       </c>
       <c r="I79" t="n">
         <v>-0.5951</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.6604</v>
+        <v>-1.6419</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.8169</v>
+        <v>-0.8078</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.0921</v>
+        <v>-1.098</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.6604</v>
+        <v>-1.6419</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.6604</v>
+        <v>-1.6419</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.6604</v>
+        <v>-1.6419</v>
       </c>
       <c r="I80" t="n">
         <v>-1.6837</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.1633</v>
+        <v>-2.1472</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.0643</v>
+        <v>-1.0564</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.2953</v>
+        <v>-1.2994</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.1633</v>
+        <v>-2.1472</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.1633</v>
+        <v>-2.1472</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.1633</v>
+        <v>-2.1472</v>
       </c>
       <c r="I81" t="n">
         <v>-2.1835</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-2.3408</v>
+        <v>-2.3147</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.1517</v>
+        <v>-1.1388</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.367</v>
+        <v>-1.3661</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.3408</v>
+        <v>-2.3147</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.3408</v>
+        <v>-2.3147</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-2.3408</v>
+        <v>-2.3147</v>
       </c>
       <c r="I82" t="n">
         <v>-2.3736</v>
@@ -4222,25 +4222,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-2.9206</v>
+        <v>-2.9156</v>
       </c>
       <c r="C83" t="n">
-        <v>-1.4369</v>
+        <v>-1.4345</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.6012</v>
+        <v>-1.6055</v>
       </c>
       <c r="E83" t="n">
-        <v>-2.9206</v>
+        <v>-2.9156</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.3372</v>
+        <v>-0.3322</v>
       </c>
       <c r="G83" t="n">
         <v>-2.5834</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.3372</v>
+        <v>-0.3322</v>
       </c>
       <c r="I83" t="n">
         <v>-0.3435</v>
